--- a/forms/trg/Formulir_TRG_ethnicfood.xlsx
+++ b/forms/trg/Formulir_TRG_ethnicfood.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B17)</f>
+        <f>COUNTA(Anggota!B5:B18)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F17)</f>
+        <f>COUNTA(Anggota!F5:F18)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Meta Mahendradatta</t>
+          <t>Prof. Dr. Ir. Abu Bakar</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Instansi xxxxx</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>/Focus</t>
+          <t>/Focus; Instansi xxxxx</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -948,10 +944,26 @@
       <c r="A6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="12" t="n"/>
-      <c r="C6" s="12" t="n"/>
-      <c r="D6" s="12" t="n"/>
-      <c r="E6" s="11" t="n"/>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Prof. Dr. Ir. Meta Mahendradatta</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Instansi xxxxx</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>/Focus</t>
+        </is>
+      </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
@@ -959,7 +971,11 @@
       <c r="J6" s="12" t="n"/>
       <c r="K6" s="12" t="n"/>
       <c r="L6" s="12" t="n"/>
-      <c r="M6" s="12" t="n"/>
+      <c r="M6" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -1148,15 +1164,32 @@
       <c r="L17" s="12" t="n"/>
       <c r="M17" s="12" t="n"/>
     </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="12" t="n"/>
+      <c r="G18" s="12" t="n"/>
+      <c r="H18" s="12" t="n"/>
+      <c r="I18" s="12" t="n"/>
+      <c r="J18" s="12" t="n"/>
+      <c r="K18" s="12" t="n"/>
+      <c r="L18" s="12" t="n"/>
+      <c r="M18" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
